--- a/artfynd/A 8188-2026 artfynd.xlsx
+++ b/artfynd/A 8188-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1009,6 +1009,103 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133645784</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58119</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>787185</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7248523</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8188-2026 artfynd.xlsx
+++ b/artfynd/A 8188-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130081469</v>
+        <v>133419441</v>
       </c>
       <c r="B2" t="n">
-        <v>58198</v>
+        <v>57975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,26 +703,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Blåsmark, Nb</t>
+          <t>Ryggmyran, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>787222</v>
+        <v>787240</v>
       </c>
       <c r="R2" t="n">
-        <v>7248516</v>
+        <v>7248566</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +748,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>05:14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>05:14</t>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Skalad liggande gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,76 +770,68 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133420715</v>
+        <v>133247754</v>
       </c>
       <c r="B3" t="n">
-        <v>58461</v>
+        <v>57162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103018</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bräntberget, Nb</t>
+          <t>Bräntberget, Bräntberget, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>787170</v>
+        <v>787240</v>
       </c>
       <c r="R3" t="n">
-        <v>7248610</v>
+        <v>7248751</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,6 +861,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På hällmark. Lämplig plats för tjäderlek?</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133419441</v>
+        <v>133247985</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>58410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,45 +903,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ryggmyran, Nb</t>
+          <t>Ryggmyran, Ryggmyran, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>787240</v>
+        <v>787252</v>
       </c>
       <c r="R4" t="n">
-        <v>7248566</v>
+        <v>7248519</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,11 +972,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Skalad liggande gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,45 +998,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133645784</v>
+        <v>130081469</v>
       </c>
       <c r="B5" t="n">
-        <v>58136</v>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>787185</v>
+        <v>787222</v>
       </c>
       <c r="R5" t="n">
-        <v>7248523</v>
+        <v>7248516</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,12 +1072,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>05:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>05:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,6 +1099,7 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1105,6 +1112,321 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133420715</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bräntberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>787170</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7248610</v>
+      </c>
+      <c r="S6" t="n">
+        <v>75</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133645784</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>787185</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7248523</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133420710</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58596</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bräntberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>787170</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7248610</v>
+      </c>
+      <c r="S8" t="n">
+        <v>75</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8188-2026 artfynd.xlsx
+++ b/artfynd/A 8188-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133419441</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133247754</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133247985</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130081469</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133420715</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133645784</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1427,8 +1462,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133420710</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>